--- a/muestras/excel/muestra-plataforma-empresa.xlsx
+++ b/muestras/excel/muestra-plataforma-empresa.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,6 +722,114 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>20000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45668</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1035000</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EDESUR luz enero</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>30111222333</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1015000</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>EPEC luz enero</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30111222333</t>
         </is>
       </c>
     </row>
